--- a/importaciones_productos/FEE90326 registro productos.xlsx
+++ b/importaciones_productos/FEE90326 registro productos.xlsx
@@ -66,15 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -443,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -503,12 +500,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AMITEAg</t>
+          <t>VITATOC99Pg</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AMINOACIDO L - TEANINA</t>
+          <t>VITAMINA E ATFA 99% USP</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -522,337 +519,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>168.98</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>COLPOLHIDg</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>COLAGENO EN POLVO HIDROLIZADO</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>45.22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>AMITRIg</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>AMINOACIDO L - TRIPTOFANO</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>116.62</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>AMICARFUMg</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>AMINOACIDO L - CARNITINA FUMARATO</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>168.98</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ALUALLg</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ALULOSA/ALLULOSE</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>28.56</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>CITMAGFCCg</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>CITRATO DE MAGNESIO FCC/MAGNESIUM CITRATE</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>CITPOTPOTg</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>CITRATO DE POTASIO/POTASSIUM CITRATE</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>VITATF99%g</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>VITAMINA E ATFA 99% USP</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
         <v>192</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>VITACE500g</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>VITAMINA A ACETATO 500.000 WS USP</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>INU90%g</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>INULINA 90%</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>30.94</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>P-Producto</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>PROCONSUEg</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>PROTEINA CONCENTRADA DE SUERO 80% WPC (LW)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>GRM</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>63.07</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +540,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>INSTRUCCIONES PARA CARGAR EN SIIGO</t>
         </is>
